--- a/final apps/BI/UAT/UAT_BI_TestScript.xlsx
+++ b/final apps/BI/UAT/UAT_BI_TestScript.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grid Features" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin Param Spec" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API &amp; Security" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage maintenance" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1688,4 +1689,1206 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Suite</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BI-ST-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Browser edge and language checks</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Storage figures render</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-browser/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BI-ST-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Browser edge and language checks</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Retention displayed</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-browser/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BI-ST-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Browser edge and language checks</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Largest reports displayed</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-browser/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BI-ST-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Browser edge and language checks</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Audit has exact removed size</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-browser/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BI-ST-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Browser edge and language checks</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Worker polling does not repeatedly scan storage</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-browser/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BI-ST-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Browser edge and language checks</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Manual refresh reloads storage</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-browser/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BI-ST-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Browser edge and language checks</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>en no untranslated storage keys</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-browser/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BI-ST-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Browser edge and language checks</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>en fits 1535px</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-browser/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BI-ST-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Browser edge and language checks</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>en fits 768px</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-browser/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BI-ST-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Browser edge and language checks</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>en fits 390px</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-browser/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BI-ST-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Browser edge and language checks</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ar no untranslated storage keys</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-browser/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BI-ST-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Browser edge and language checks</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ar fits 1535px</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-browser/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BI-ST-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Browser edge and language checks</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ar fits 768px</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-browser/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BI-ST-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Browser edge and language checks</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ar fits 390px</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-browser/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BI-ST-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Browser edge and language checks</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Failure shown without losing previous data</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-browser/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BI-ST-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Browser edge and language checks</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Empty reports and audit states</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-browser/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BI-ST-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Browser edge and language checks</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Keep-forever state renders</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-browser/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BI-ST-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Browser edge and language checks</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Failed banner clears on retry</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-browser/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BI-ST-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Browser edge and language checks</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Failed cleanup visible</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-browser/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BI-ST-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Browser edge and language checks</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Error text safely escaped</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-browser/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BI-ST-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Browser edge and language checks</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>No JavaScript errors</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-browser/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BI-ST-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Live API and access</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Storage panel loads real data</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-live/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BI-ST-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Live API and access</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Authenticated storage API returns 200</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-live/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BI-ST-024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Live API and access</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Retention remains 90 days</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-live/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BI-ST-025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Live API and access</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Storage totals are plausible</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-live/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BI-ST-026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Live API and access</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Cleanup audit is present</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-live/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BI-ST-027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Live API and access</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>At most 10 largest reports and 20 audits</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-live/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BI-ST-028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Live API and access</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>File bytes reconcile with all listed reports when fewer than 10</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-live/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BI-ST-029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Live API and access</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Anonymous storage API blocked</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-live/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BI-ST-030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Live API and access</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Existing scheduler controls still list maintenance</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-live/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BI-ST-031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Live API and access</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Non-admin storage API blocked</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/deployed-live/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BI-ST-032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Database cleanup</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Retention unchanged at 90</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/db-test.log</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BI-ST-033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Database cleanup</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>No real outputs eligible before fixture</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/db-test.log</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BI-ST-034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Database cleanup</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Only expired fixture removed</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/db-test.log</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BI-ST-035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Database cleanup</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Run history preserved</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/db-test.log</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BI-ST-036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Database cleanup</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Audit records success and exact file count</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/db-test.log</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BI-ST-037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Database cleanup</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Audit records exact bytes</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/db-test.log</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BI-ST-038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Database cleanup</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Audit records timing and policy</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/db-test.log</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BI-ST-039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Database cleanup</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>All real outputs preserved</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/db-test.log</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BI-ST-040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Database cleanup</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Repeated cleanup safely records zero deletions</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/db-test.log</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BI-ST-041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Database cleanup</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Exactly one enabled maintenance schedule</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/db-test.log</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BI-ST-042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Database cleanup</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BI-managed ADMIN schedule retained</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/db-test.log</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BI-ST-SCHED</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Scheduler</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>New audited procedure executed successfully on the retained 15-minute ADMIN schedule; duplicate disabled</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>evidence_06-Sep-2026-01/final-check.log</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>